--- a/add-info-dmp/ig/StructureDefinition-ActorPS.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-ActorPS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-19T16:11:49+00:00</t>
+    <t>2025-08-01T13:09:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,9 @@
     <t>Description</t>
   </si>
   <si>
-    <t xml:space="preserve">Cet attribut représente un acteur PS. </t>
+    <t xml:space="preserve">
+Cet attribut représente un acteur PS.
+</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -231,7 +233,7 @@
     <t>Constraint(s)</t>
   </si>
   <si>
-    <t>Mapping: null</t>
+    <t>Mapping: ActorXDSCDA</t>
   </si>
   <si>
     <t/>
@@ -378,7 +380,7 @@
 </t>
   </si>
   <si>
-    <t>Type de nom : Valeur en fonction de l’auteur :  D, pour les personnes physiques, • U, pour les systèmes.</t>
+    <t>Type de nom : Valeur en fonction de l’auteur :  D, pour les personnes physiques, -U, pour les systèmes.</t>
   </si>
   <si>
     <t>D</t>

--- a/add-info-dmp/ig/StructureDefinition-ActorPS.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-ActorPS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-01T13:09:58+00:00</t>
+    <t>2025-08-04T10:11:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-ActorPS.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-ActorPS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-04T10:11:31+00:00</t>
+    <t>2025-08-04T13:10:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-ActorPS.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-ActorPS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-04T13:10:17+00:00</t>
+    <t>2026-06-10T15:39:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -110,7 +110,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/pdsm4dmp/StructureDefinition/ActorXDS</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/pdsm4dmp/StructureDefinition/ActorXDS|0.1.0</t>
   </si>
   <si>
     <t>Abstract</t>

--- a/add-info-dmp/ig/StructureDefinition-ActorPS.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-ActorPS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T15:39:40+00:00</t>
+    <t>2026-06-10T15:45:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -75,7 +75,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>

--- a/add-info-dmp/ig/StructureDefinition-ActorPS.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-ActorPS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T15:45:32+00:00</t>
+    <t>2026-06-10T15:59:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-ActorPS.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-ActorPS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T15:59:45+00:00</t>
+    <t>2026-06-10T16:12:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-ActorPS.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-ActorPS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T16:12:06+00:00</t>
+    <t>2026-06-10T16:18:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-ActorPS.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-ActorPS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T16:18:52+00:00</t>
+    <t>2026-06-11T15:47:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-ActorPS.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-ActorPS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T15:47:13+00:00</t>
+    <t>2026-06-11T15:59:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-ActorPS.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-ActorPS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T15:59:09+00:00</t>
+    <t>2026-06-11T16:49:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-ActorPS.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-ActorPS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T16:49:00+00:00</t>
+    <t>2026-06-12T14:52:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-ActorPS.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-ActorPS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:52:39+00:00</t>
+    <t>2026-06-12T14:55:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-ActorPS.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-ActorPS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:55:33+00:00</t>
+    <t>2026-06-12T14:56:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-ActorPS.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-ActorPS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:56:09+00:00</t>
+    <t>2026-06-12T14:58:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-ActorPS.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-ActorPS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:58:42+00:00</t>
+    <t>2026-06-12T15:04:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-ActorPS.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-ActorPS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T15:04:49+00:00</t>
+    <t>2026-06-12T15:09:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-ActorPS.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-ActorPS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T15:09:19+00:00</t>
+    <t>2026-06-12T15:31:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-ActorPS.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-ActorPS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T15:31:20+00:00</t>
+    <t>2026-06-12T15:45:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-ActorPS.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-ActorPS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T15:45:22+00:00</t>
+    <t>2026-06-12T16:24:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-ActorPS.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-ActorPS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T16:24:39+00:00</t>
+    <t>2026-06-16T12:17:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-ActorPS.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-ActorPS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T12:17:15+00:00</t>
+    <t>2026-06-16T12:25:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-ActorPS.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-ActorPS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T12:25:33+00:00</t>
+    <t>2026-06-17T07:47:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-ActorPS.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-ActorPS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T07:47:53+00:00</t>
+    <t>2026-06-17T07:58:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-ActorPS.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-ActorPS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T07:58:49+00:00</t>
+    <t>2026-06-17T08:05:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-ActorPS.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-ActorPS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T08:05:28+00:00</t>
+    <t>2026-06-17T08:38:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-ActorPS.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-ActorPS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T08:38:09+00:00</t>
+    <t>2026-06-17T08:46:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-ActorPS.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-ActorPS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T08:46:38+00:00</t>
+    <t>2026-06-17T08:50:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-ActorPS.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-ActorPS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T08:50:19+00:00</t>
+    <t>2026-06-17T11:32:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-ActorPS.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-ActorPS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T11:32:53+00:00</t>
+    <t>2026-06-17T11:35:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-ActorPS.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-ActorPS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T11:35:28+00:00</t>
+    <t>2026-06-17T11:36:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-ActorPS.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-ActorPS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T11:36:10+00:00</t>
+    <t>2026-06-17T12:12:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
